--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
@@ -1295,8 +1295,7 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>実際の結果値  
-【JP Core仕様】component要素を利用して複数の結果を表現することを考慮しているため、本要素は使用しない</t>
+    <t>実際の結果値 【JP Core仕様】component要素を利用して複数の結果を表現することを考慮しているため、本要素は使用しない</t>
   </si>
   <si>
     <t>観察にはあります。1）ここでの単一の値、2）関連する値とコンポーネント値のセット、または3）関連またはコンポーネント値のセットのみ。値が存在する場合、この要素のデータ型は、viscervation.codeによって決定する必要があります。フィールドが通常コーディングされている場合、または観測に関連付けられたタイプの場合、文字列の代わりにテキストのみを持つCodeableconecteが使用されます。コードはコード化された値を定義します。追加のガイダンスについては、以下の[[メモ]セクション]（[観察.html＃注）を参照してください。 / An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -1412,8 +1411,7 @@
     <t>Observation.bodySite</t>
   </si>
   <si>
-    <t>観察された身体部位  
-【JP Core仕様】特定の歯（歯式）を指定</t>
+    <t>観察された身体部位 【JP Core仕様】特定の歯（歯式）を指定</t>
   </si>
   <si>
     <t>観察結果で見つかったコードで暗黙的ではない場合にのみ使用されます。多くのシステムでは、これはインラインコンポーネントの代わりに関連する観察として表される場合があります。
@@ -1467,8 +1465,7 @@
 </t>
   </si>
   <si>
-    <t>観察（観測、検査）に使われた検体材料
-【JP Core仕様】未使用</t>
+    <t>観察（観測、検査）に使われた検体材料 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>`Observation.code`にあるコードで暗黙的に示されない場合にのみ使用する必要がある。検体自体の観察は行われない。観察（観測、検査）対象者に対して実施されるが、多くの場合には対象者から得られた検体に対して実施される。検体が奥の場合に関わるが、それらは常に追跡され、明示的に報告されるとは限らないことに注意すること。またobservationリソースは、検体を明示的に記述するような状況下（診断レポートなど）で使用される場合があることに注意。</t>
@@ -1707,8 +1704,7 @@
 </t>
   </si>
   <si>
-    <t>observationの発生源に関連する測定
-【JP Core仕様】未使用</t>
+    <t>observationの発生源に関連する測定 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>この要素にリストされているすべての参照の選択肢は、派生値の元のデータなる可能性のある臨床観察やその他の測定値を表すことができる。最も一般的な参照先は、別のobservationである。observationをグループに一緒にまとめる方法については、以下の[メモ]（observation.html＃obsgrouping）を参照すること。</t>
@@ -1720,8 +1716,7 @@
     <t>Observation.component</t>
   </si>
   <si>
-    <t>複合的な結果
-【JP Core仕様】特定の現存歯の処置状態</t>
+    <t>複合的な結果 【JP Core仕様】特定の現存歯の処置状態</t>
   </si>
   <si>
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
@@ -11830,7 +11825,7 @@
         <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>83</v>
@@ -13030,7 +13025,7 @@
         <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>83</v>
